--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO BALANÇA - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO BALANÇA - 02_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,98 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>63</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>602883759619</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>EIXO GARFO TRASEIRO IRON POP100-110 184422</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>64</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>7894152034876</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>EIXO GARFO TRASEIRO DANIDREA XTZ250/ XTZ150</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>65</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>7899468058547</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ROLAMENT BALANÇA TRILHA XTZ125 2003 A 2014/ XTZ150 2019 A 2023/ XTZ250</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>66</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>4896061</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ROLAMENT BALANÇA NXR125-150-160/ XRE190-300/ XR250</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO BALANÇA - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/EIXO BALANÇA - 02_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,11 +492,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,7 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,7 +532,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -570,11 +552,10 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -589,17 +570,12 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -616,11 +592,10 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -637,11 +612,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -658,11 +632,10 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -679,11 +652,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -700,11 +672,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -721,11 +692,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -742,11 +712,10 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
@@ -759,11 +728,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
@@ -776,11 +744,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
@@ -793,11 +760,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
@@ -810,11 +776,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -829,17 +794,12 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
@@ -852,11 +812,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
@@ -869,15 +828,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -892,11 +846,6 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>76</t>
         </is>
       </c>
     </row>
